--- a/data/Creatine/doma2022/doma2022_creatine_48h_post_protocol.xlsx
+++ b/data/Creatine/doma2022/doma2022_creatine_48h_post_protocol.xlsx
@@ -101,7 +101,7 @@
     <t>se_g</t>
   </si>
   <si>
-    <t>SMD</t>
+    <t>d</t>
   </si>
   <si>
     <t>Veggi</t>
